--- a/consent_forms/014_facility_rules_and_regulations_acknowledgment--consent_forms.xlsx
+++ b/consent_forms/014_facility_rules_and_regulations_acknowledgment--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,36 +525,40 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Facility Rules And Regulations</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your name?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide your name as it appears on your ID.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>facility_rules_and_regulations_acknowledgment</t>
+          <t>contact_information</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>What is your contact information?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,12 +570,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>facility_rules_and_regulations_acknowledgment</t>
+          <t>questions_and_concerns</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Do you have any questions or concerns about the facility's rules and regulations?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,23 +588,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>facility_rules_and_regulations_acknowledgment</t>
+          <t>rules_understood</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Have you read and understood the facility's rules and regulations?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +616,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>facility_rules_and_regulations_acknowledgment</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Facility Rules And Regulations</t>
+          <t>What is your role at the facility?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,12 +639,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>facility_rules_and_regulations_acknowledgment</t>
+          <t>allergies_restrictions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rules</t>
+          <t>Do you have any dietary restrictions or allergies that the facility should be aware of?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,23 +657,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>facility_rules_and_regulations_acknowledgment</t>
+          <t>emergency_exits</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Are you aware of the emergency exits and emergency procedures in the facility?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,85 +685,131 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>facility_rules_and_regulations_acknowledgment</t>
+          <t>facility_resources</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>How will you be using the facility's resources and facilities?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>facility_rules_and_regulations_acknowledgment</t>
+          <t>equipment_training</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Facility Rules And Regulations</t>
+          <t>Have you received training on the use of the facility's equipment and resources?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>facility_rules_and_regulations_acknowledgment</t>
+          <t>consequences</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>facility_rules_and_regulations</t>
+          <t>Do you understand the consequences of not following the facility's rules and regulations?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>facility_rules_and_regulations</t>
+          <t>incident_reporting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>facility_rules_and_regulations</t>
+          <t>Are you aware of the facility's policies on reporting incidents or near misses?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>consent</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Do you agree to abide by the facility's rules and regulations?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>additional_comments</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Is there anything else you'd like to add or discuss about the facility's rules and regulations?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -776,12 +826,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -804,34 +854,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>facility_rules_and_regulations_acknowledgment_choices</t>
+          <t>rules_understood_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>facility_rules_and_regulations_acknowledgment_choices</t>
+          <t>rules_understood_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>emergency_exits_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>emergency_exits_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>equipment_training_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>equipment_training_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>consequences_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>consequences_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>incident_reporting_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>incident_reporting_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
